--- a/아오모리_아키타_여행일정표_통합.xlsx
+++ b/아오모리_아키타_여행일정표_통합.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="243">
   <si>
     <t xml:space="preserve">항목</t>
   </si>
@@ -3957,7 +3957,77 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">13:00~17:00</t>
+    <t xml:space="preserve">점심 — 히로사키 시내</t>
+  </si>
+  <si>
+    <t xml:space="preserve">히로사키성 인근</t>
+  </si>
+  <si>
+    <t xml:space="preserve">弘前城 そば ランチ</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">전날 이나니와우동</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">면</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">과 겹치지 않게</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">국수 아닌 옵션도 추가해둠</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">14:00~17:00</t>
   </si>
   <si>
     <r>
@@ -5866,7 +5936,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="7" t="n">
-        <v>3218031</v>
+        <v>3237611</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>10</v>
@@ -5878,7 +5948,7 @@
       </c>
       <c r="B6" s="7" t="n">
         <f aca="false">B5/2</f>
-        <v>1609015.5</v>
+        <v>1618805.5</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>12</v>
@@ -5998,7 +6068,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M67"/>
+  <dimension ref="A1:M68"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -7292,35 +7362,37 @@
         <v>12</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="14" t="n">
+    <row r="47" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14" t="s">
+      <c r="B47" s="23"/>
+      <c r="C47" s="23"/>
+      <c r="D47" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="E47" s="24" t="s">
+        <v>55</v>
+      </c>
+      <c r="F47" s="25" t="s">
         <v>199</v>
       </c>
-      <c r="E47" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="F47" s="18" t="s">
+      <c r="G47" s="24" t="s">
         <v>200</v>
       </c>
-      <c r="G47" s="15" t="s">
+      <c r="H47" s="26" t="n">
+        <v>2200</v>
+      </c>
+      <c r="I47" s="26"/>
+      <c r="J47" s="23"/>
+      <c r="K47" s="24" t="s">
         <v>201</v>
       </c>
-      <c r="H47" s="17"/>
-      <c r="I47" s="17"/>
-      <c r="J47" s="14"/>
-      <c r="K47" s="15" t="s">
+      <c r="L47" s="25" t="s">
         <v>202</v>
       </c>
-      <c r="L47" s="18" t="s">
-        <v>203</v>
-      </c>
-      <c r="M47" s="14" t="s">
-        <v>12</v>
+      <c r="M47" s="24" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7330,180 +7402,180 @@
       <c r="B48" s="14"/>
       <c r="C48" s="14"/>
       <c r="D48" s="14" t="s">
+        <v>203</v>
+      </c>
+      <c r="E48" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="F48" s="18" t="s">
         <v>204</v>
       </c>
-      <c r="E48" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="F48" s="18" t="s">
+      <c r="G48" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="G48" s="14"/>
       <c r="H48" s="17"/>
       <c r="I48" s="17"/>
       <c r="J48" s="14"/>
       <c r="K48" s="15" t="s">
         <v>206</v>
       </c>
-      <c r="L48" s="16"/>
+      <c r="L48" s="18" t="s">
+        <v>207</v>
+      </c>
       <c r="M48" s="14" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="14" t="n">
         <v>5</v>
       </c>
       <c r="B49" s="14"/>
       <c r="C49" s="14"/>
       <c r="D49" s="14" t="s">
-        <v>70</v>
+        <v>208</v>
       </c>
       <c r="E49" s="15" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="F49" s="18" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="G49" s="14"/>
-      <c r="H49" s="17" t="n">
-        <v>3000</v>
-      </c>
+      <c r="H49" s="17"/>
       <c r="I49" s="17"/>
       <c r="J49" s="14"/>
       <c r="K49" s="15" t="s">
-        <v>208</v>
-      </c>
-      <c r="L49" s="18" t="s">
-        <v>209</v>
-      </c>
+        <v>210</v>
+      </c>
+      <c r="L49" s="16"/>
       <c r="M49" s="14" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="19" t="n">
+    <row r="50" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B50" s="19"/>
-      <c r="C50" s="19"/>
-      <c r="D50" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="E50" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="F50" s="21" t="s">
-        <v>210</v>
-      </c>
-      <c r="G50" s="19" t="s">
-        <v>152</v>
-      </c>
-      <c r="H50" s="22" t="n">
-        <v>19953.82</v>
-      </c>
-      <c r="I50" s="22"/>
-      <c r="J50" s="19"/>
-      <c r="K50" s="20" t="s">
-        <v>206</v>
-      </c>
-      <c r="L50" s="21" t="s">
+      <c r="B50" s="14"/>
+      <c r="C50" s="14"/>
+      <c r="D50" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="E50" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F50" s="18" t="s">
         <v>211</v>
       </c>
-      <c r="M50" s="20" t="s">
-        <v>51</v>
+      <c r="G50" s="14"/>
+      <c r="H50" s="17" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I50" s="17"/>
+      <c r="J50" s="14"/>
+      <c r="K50" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="L50" s="18" t="s">
+        <v>213</v>
+      </c>
+      <c r="M50" s="14" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="28"/>
-      <c r="B51" s="28"/>
-      <c r="C51" s="28"/>
-      <c r="D51" s="28"/>
-      <c r="E51" s="28"/>
-      <c r="F51" s="28" t="s">
-        <v>212</v>
-      </c>
-      <c r="G51" s="28"/>
-      <c r="H51" s="29" t="n">
-        <f aca="false">SUM(H45:H50)</f>
-        <v>25954.82</v>
-      </c>
-      <c r="I51" s="29" t="n">
-        <f aca="false">SUM(I45:I50)</f>
+      <c r="A51" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="B51" s="19"/>
+      <c r="C51" s="19"/>
+      <c r="D51" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="E51" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="F51" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="G51" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="H51" s="22" t="n">
+        <v>19953.82</v>
+      </c>
+      <c r="I51" s="22"/>
+      <c r="J51" s="19"/>
+      <c r="K51" s="20" t="s">
+        <v>210</v>
+      </c>
+      <c r="L51" s="21" t="s">
+        <v>215</v>
+      </c>
+      <c r="M51" s="20" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="28"/>
+      <c r="B52" s="28"/>
+      <c r="C52" s="28"/>
+      <c r="D52" s="28"/>
+      <c r="E52" s="28"/>
+      <c r="F52" s="28" t="s">
+        <v>216</v>
+      </c>
+      <c r="G52" s="28"/>
+      <c r="H52" s="29" t="n">
+        <f aca="false">SUM(H45:H51)</f>
+        <v>28154.82</v>
+      </c>
+      <c r="I52" s="29" t="n">
+        <f aca="false">SUM(I45:I51)</f>
         <v>0</v>
       </c>
-      <c r="J51" s="28"/>
-      <c r="K51" s="28"/>
-      <c r="L51" s="28"/>
-      <c r="M51" s="28"/>
+      <c r="J52" s="28"/>
+      <c r="K52" s="28"/>
+      <c r="L52" s="28"/>
+      <c r="M52" s="28"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="14" t="n">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B53" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="C53" s="15" t="s">
-        <v>214</v>
-      </c>
-      <c r="D53" s="14" t="s">
-        <v>215</v>
-      </c>
-      <c r="E53" s="15" t="s">
+      <c r="B54" s="14" t="s">
+        <v>217</v>
+      </c>
+      <c r="C54" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="D54" s="14" t="s">
+        <v>219</v>
+      </c>
+      <c r="E54" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="F53" s="18" t="s">
-        <v>216</v>
-      </c>
-      <c r="G53" s="14"/>
-      <c r="H53" s="17"/>
-      <c r="I53" s="17"/>
-      <c r="J53" s="14"/>
-      <c r="K53" s="15" t="s">
-        <v>206</v>
-      </c>
-      <c r="L53" s="18" t="s">
-        <v>217</v>
-      </c>
-      <c r="M53" s="14" t="s">
+      <c r="F54" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="G54" s="14"/>
+      <c r="H54" s="17"/>
+      <c r="I54" s="17"/>
+      <c r="J54" s="14"/>
+      <c r="K54" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="L54" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="M54" s="14" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="19" t="n">
+    <row r="55" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="19" t="n">
         <v>2</v>
-      </c>
-      <c r="B54" s="19"/>
-      <c r="C54" s="19"/>
-      <c r="D54" s="19" t="s">
-        <v>218</v>
-      </c>
-      <c r="E54" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="F54" s="21" t="s">
-        <v>219</v>
-      </c>
-      <c r="G54" s="19"/>
-      <c r="H54" s="22" t="n">
-        <v>1500</v>
-      </c>
-      <c r="I54" s="22"/>
-      <c r="J54" s="19"/>
-      <c r="K54" s="20" t="s">
-        <v>220</v>
-      </c>
-      <c r="L54" s="21" t="s">
-        <v>221</v>
-      </c>
-      <c r="M54" s="20" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="19" t="n">
-        <v>3</v>
       </c>
       <c r="B55" s="19"/>
       <c r="C55" s="19"/>
@@ -7511,131 +7583,145 @@
         <v>222</v>
       </c>
       <c r="E55" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="F55" s="21" t="s">
         <v>223</v>
       </c>
-      <c r="F55" s="21" t="s">
-        <v>224</v>
-      </c>
-      <c r="G55" s="20" t="s">
-        <v>225</v>
-      </c>
+      <c r="G55" s="19"/>
       <c r="H55" s="22" t="n">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="I55" s="22"/>
       <c r="J55" s="19"/>
-      <c r="K55" s="19"/>
+      <c r="K55" s="20" t="s">
+        <v>224</v>
+      </c>
       <c r="L55" s="21" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="M55" s="20" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14" t="s">
+      <c r="A56" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="B56" s="19"/>
+      <c r="C56" s="19"/>
+      <c r="D56" s="19" t="s">
+        <v>226</v>
+      </c>
+      <c r="E56" s="20" t="s">
         <v>227</v>
       </c>
-      <c r="E56" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="F56" s="16" t="s">
+      <c r="F56" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="G56" s="14"/>
-      <c r="H56" s="17"/>
-      <c r="I56" s="17"/>
-      <c r="J56" s="14"/>
-      <c r="K56" s="14"/>
-      <c r="L56" s="18" t="s">
+      <c r="G56" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="M56" s="14" t="s">
-        <v>12</v>
+      <c r="H56" s="22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I56" s="22"/>
+      <c r="J56" s="19"/>
+      <c r="K56" s="19"/>
+      <c r="L56" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="M56" s="20" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="28"/>
-      <c r="B57" s="28"/>
-      <c r="C57" s="28"/>
-      <c r="D57" s="28"/>
-      <c r="E57" s="28"/>
-      <c r="F57" s="28" t="s">
-        <v>230</v>
-      </c>
-      <c r="G57" s="28"/>
-      <c r="H57" s="29" t="n">
-        <f aca="false">SUM(H53:H56)</f>
+      <c r="A57" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B57" s="14"/>
+      <c r="C57" s="14"/>
+      <c r="D57" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="E57" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="F57" s="16" t="s">
+        <v>232</v>
+      </c>
+      <c r="G57" s="14"/>
+      <c r="H57" s="17"/>
+      <c r="I57" s="17"/>
+      <c r="J57" s="14"/>
+      <c r="K57" s="14"/>
+      <c r="L57" s="18" t="s">
+        <v>233</v>
+      </c>
+      <c r="M57" s="14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="28"/>
+      <c r="B58" s="28"/>
+      <c r="C58" s="28"/>
+      <c r="D58" s="28"/>
+      <c r="E58" s="28"/>
+      <c r="F58" s="28" t="s">
+        <v>234</v>
+      </c>
+      <c r="G58" s="28"/>
+      <c r="H58" s="29" t="n">
+        <f aca="false">SUM(H54:H57)</f>
         <v>2500</v>
       </c>
-      <c r="I57" s="29" t="n">
-        <f aca="false">SUM(I53:I56)</f>
+      <c r="I58" s="29" t="n">
+        <f aca="false">SUM(I54:I57)</f>
         <v>0</v>
       </c>
-      <c r="J57" s="28"/>
-      <c r="K57" s="28"/>
-      <c r="L57" s="28"/>
-      <c r="M57" s="28"/>
+      <c r="J58" s="28"/>
+      <c r="K58" s="28"/>
+      <c r="L58" s="28"/>
+      <c r="M58" s="28"/>
     </row>
-    <row r="59" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="6"/>
-      <c r="B59" s="6"/>
-      <c r="C59" s="6"/>
-      <c r="D59" s="6"/>
-      <c r="E59" s="6"/>
-      <c r="F59" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="G59" s="6"/>
-      <c r="H59" s="7" t="n">
-        <f aca="false">H11+H22+H33+H43+H51+H57</f>
-        <v>169961.3</v>
-      </c>
-      <c r="I59" s="7" t="n">
-        <f aca="false">I11+I22+I33+I43+I51+I57</f>
+    <row r="60" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="6"/>
+      <c r="B60" s="6"/>
+      <c r="C60" s="6"/>
+      <c r="D60" s="6"/>
+      <c r="E60" s="6"/>
+      <c r="F60" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="G60" s="6"/>
+      <c r="H60" s="7" t="n">
+        <f aca="false">H11+H22+H33+H43+H52+H58</f>
+        <v>172161.3</v>
+      </c>
+      <c r="I60" s="7" t="n">
+        <f aca="false">I11+I22+I33+I43+I52+I58</f>
         <v>0</v>
       </c>
-      <c r="J59" s="6"/>
-      <c r="K59" s="6"/>
-      <c r="L59" s="6"/>
-      <c r="M59" s="6"/>
+      <c r="J60" s="6"/>
+      <c r="K60" s="6"/>
+      <c r="L60" s="6"/>
+      <c r="M60" s="6"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="30" t="s">
-        <v>232</v>
-      </c>
-      <c r="B61" s="31" t="s">
-        <v>233</v>
-      </c>
-      <c r="D61" s="32" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="33" t="s">
-        <v>235</v>
-      </c>
-      <c r="B63" s="33"/>
-      <c r="C63" s="33"/>
-      <c r="D63" s="33"/>
-      <c r="E63" s="33"/>
-      <c r="F63" s="33"/>
-      <c r="G63" s="33"/>
-      <c r="H63" s="33"/>
-      <c r="I63" s="33"/>
-      <c r="J63" s="33"/>
-      <c r="K63" s="33"/>
-      <c r="L63" s="33"/>
-      <c r="M63" s="33"/>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="B62" s="31" t="s">
+        <v>237</v>
+      </c>
+      <c r="D62" s="32" t="s">
+        <v>238</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="33" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B64" s="33"/>
       <c r="C64" s="33"/>
@@ -7651,25 +7737,25 @@
       <c r="M64" s="33"/>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="9" t="s">
-        <v>237</v>
-      </c>
-      <c r="B65" s="9"/>
-      <c r="C65" s="9"/>
-      <c r="D65" s="9"/>
-      <c r="E65" s="9"/>
-      <c r="F65" s="9"/>
-      <c r="G65" s="9"/>
-      <c r="H65" s="9"/>
-      <c r="I65" s="9"/>
-      <c r="J65" s="9"/>
-      <c r="K65" s="9"/>
-      <c r="L65" s="9"/>
-      <c r="M65" s="9"/>
+      <c r="A65" s="33" t="s">
+        <v>240</v>
+      </c>
+      <c r="B65" s="33"/>
+      <c r="C65" s="33"/>
+      <c r="D65" s="33"/>
+      <c r="E65" s="33"/>
+      <c r="F65" s="33"/>
+      <c r="G65" s="33"/>
+      <c r="H65" s="33"/>
+      <c r="I65" s="33"/>
+      <c r="J65" s="33"/>
+      <c r="K65" s="33"/>
+      <c r="L65" s="33"/>
+      <c r="M65" s="33"/>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="9" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B66" s="9"/>
       <c r="C66" s="9"/>
@@ -7686,7 +7772,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="9" t="s">
-        <v>14</v>
+        <v>242</v>
       </c>
       <c r="B67" s="9"/>
       <c r="C67" s="9"/>
@@ -7701,13 +7787,30 @@
       <c r="L67" s="9"/>
       <c r="M67" s="9"/>
     </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B68" s="9"/>
+      <c r="C68" s="9"/>
+      <c r="D68" s="9"/>
+      <c r="E68" s="9"/>
+      <c r="F68" s="9"/>
+      <c r="G68" s="9"/>
+      <c r="H68" s="9"/>
+      <c r="I68" s="9"/>
+      <c r="J68" s="9"/>
+      <c r="K68" s="9"/>
+      <c r="L68" s="9"/>
+      <c r="M68" s="9"/>
+    </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A63:M63"/>
     <mergeCell ref="A64:M64"/>
     <mergeCell ref="A65:M65"/>
     <mergeCell ref="A66:M66"/>
     <mergeCell ref="A67:M67"/>
+    <mergeCell ref="A68:M68"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
